--- a/OpenCart-TestExecution/OpenCart_Test Execution.xlsx
+++ b/OpenCart-TestExecution/OpenCart_Test Execution.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fd2f30a4efa5a7af/Desktop/Open Cart Excel Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{10F8E734-299F-452E-A73C-D9D8F4DEFAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DDE55D4-B6BD-41E0-B3A3-D197DCE2F520}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{F6BF3AE0-95ED-4F88-8C76-3FD761E1EC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B74873FE-759A-456B-B921-80DCCAE1FDE4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{B74873FE-759A-456B-B921-80DCCAE1FDE4}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
     <sheet name="REGISTER" sheetId="2" r:id="rId2"/>
     <sheet name="LOGIN" sheetId="3" r:id="rId3"/>
     <sheet name="FORGOT PASSWORD" sheetId="4" r:id="rId4"/>
+    <sheet name="SEARCH BOX" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="516">
   <si>
     <t>Project Name</t>
   </si>
@@ -1470,12 +1471,427 @@
   <si>
     <t>1. Reset Password functionality should work correctly in all the supported environments</t>
   </si>
+  <si>
+    <t>Pre-Conditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Search Functionality
+(TS_004)</t>
+  </si>
+  <si>
+    <t>TC_SF_001</t>
+  </si>
+  <si>
+    <t>Validate searching with an existing Product Name</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL 
+( https://demo.opencart.com )</t>
+  </si>
+  <si>
+    <t>1. Enter any existing product name into the 'Search' text box field 
+2. Click on the button having search icon</t>
+  </si>
+  <si>
+    <t>Product Name: iPhone</t>
+  </si>
+  <si>
+    <t>1. Searched product should be displayed in the search results</t>
+  </si>
+  <si>
+    <t>1. Searched product is displayed in the search results</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>TC_SF_002</t>
+  </si>
+  <si>
+    <t>Validate searching with a non existing Product Name</t>
+  </si>
+  <si>
+    <t>1. Enter non existing product name into the 'Search' text box field
+2. Click on the button having search icon.</t>
+  </si>
+  <si>
+    <t>Product Name: fastrack</t>
+  </si>
+  <si>
+    <t>1. 'There is no product that matches the search criteria' should be displayed in the Search Results page</t>
+  </si>
+  <si>
+    <t>1. 'There is no product that matches the search criteria' is displayed in the Search Results page</t>
+  </si>
+  <si>
+    <t>TC_SF_003</t>
+  </si>
+  <si>
+    <t>Validate searching without providing any Product Name</t>
+  </si>
+  <si>
+    <t>1. Don't enter anything into the 'Search' text box field 
+2. Click on the button having search icon</t>
+  </si>
+  <si>
+    <t>Not Applicable</t>
+  </si>
+  <si>
+    <t>1.'There is no product that matches the search criteria' should be displayed in the Search Results page</t>
+  </si>
+  <si>
+    <t>TC_SF_004</t>
+  </si>
+  <si>
+    <t>Validate searching for a product after login to the Application</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL 
+( https://demo.opencart.com )
+2. Log in to the application</t>
+  </si>
+  <si>
+    <t>Product Name: iphone</t>
+  </si>
+  <si>
+    <t>TC_SF_005</t>
+  </si>
+  <si>
+    <t>Validate searching by providing a search criteria which results in mulitple products</t>
+  </si>
+  <si>
+    <t>1. Enter the search criteria in the 'Search' text box field which can result in mutliple products
+2. Click on the button having search icon</t>
+  </si>
+  <si>
+    <t>Product Name: Mac</t>
+  </si>
+  <si>
+    <t>1. More than one products should be displayed in the search results page</t>
+  </si>
+  <si>
+    <t>1. More than one products are displayed in the search results page</t>
+  </si>
+  <si>
+    <t>TC_SF_006</t>
+  </si>
+  <si>
+    <t>Validate all the fields in the Search functionality and Search page have placeholders</t>
+  </si>
+  <si>
+    <t>1. Don't enter anything into the 'Search' text box field 
+2. Click on the button having search icon (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>1. Proper placeholder text is displayed in the below fields:
+- Search text box field
+- Search Criteria text box field</t>
+  </si>
+  <si>
+    <t>TC_SF_007</t>
+  </si>
+  <si>
+    <t>Validate searching using 'Search Criteria' field</t>
+  </si>
+  <si>
+    <t>1. Don't enter anything into the 'Search' text box field 
+2. Click on the button having search icon 
+3. Enter any existing product name into the 'Search Criteria' text box field
+4. Click on 'Search' button</t>
+  </si>
+  <si>
+    <t>TC_SF_008</t>
+  </si>
+  <si>
+    <t>Validate Search using the text from the product description</t>
+  </si>
+  <si>
+    <t>1. Don't enter anything into the 'Search' text box field 
+2. Click on the button having search icon 
+3. Enter any text from the Product Description into the 'Search Criteria' text box field - &lt;Refer Test Data&gt;
+4. Select 'Search in product descriptions' checkbox option
+5. Click on 'Search' button (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Text in Production description of iphone Product: voicemail message phone</t>
+  </si>
+  <si>
+    <t>1. Product having the given text in its description should be displayed in the search results</t>
+  </si>
+  <si>
+    <t>1. Product having the given text in its description is displayed in the search results</t>
+  </si>
+  <si>
+    <t>TC_SF_009</t>
+  </si>
+  <si>
+    <t>Validate Search by selecting the category of product</t>
+  </si>
+  <si>
+    <t>1. Don't enter anything into the 'Search' text box field 
+2. Click on the button having search icon 
+3. Enter any Product Name into the 'Search Criteria' text box field - &lt;Refer Test Data&gt;
+4. Select the correct category of the given Product Name into 'Category' dropdown field - &lt;Refer Test Data&gt;
+5. Click on 'Search' button (Validate ER-1)
+6. Select a wrong category in tthe 'Category' dropdown field - - &lt;Refer Test Data&gt;
+7. Click on 'Search' button (Validate ER-2)</t>
+  </si>
+  <si>
+    <t>Product Name: iphone
+Correct Category Name: Phone &amp; PDAs
+Wrong Category Name: mac</t>
+  </si>
+  <si>
+    <t>1. Product should be successfully displayed in the search results.
+2.There is no product that matches the search criteria' should be displayed in the Search Results page</t>
+  </si>
+  <si>
+    <t>1. Product is displayed in the search results.
+2.There is no product that matches the search criteria' is displayed in the Search Results page</t>
+  </si>
+  <si>
+    <t>TC_SF_010</t>
+  </si>
+  <si>
+    <t>Validate Search by selecting to search in subcategories</t>
+  </si>
+  <si>
+    <t>1. Don't enter anything into the 'Search' text box field 
+2. Click on the button having search icon 
+3. Enter any Product Name into the 'Search Criteria' text box field
+4. Select the Parent category of the given Product Name into 'Category' dropdown field 
+5. Click on 'Search' button
+6. Select 'Search in subcategories' checkbox field
+7. Click on 'Search' button</t>
+  </si>
+  <si>
+    <t>Product Name: iMac
+Parent Category Name: Desktops</t>
+  </si>
+  <si>
+    <t>1. 'There is no product that matches the search criteria' should be displayed in the Search Results page
+2. Searched product should be displayed in the search results</t>
+  </si>
+  <si>
+    <t>1. 'There is no product that matches the search criteria' is displayed in the Search Results page
+2. Searched product is displayed in the search results</t>
+  </si>
+  <si>
+    <t>TC_SF_011</t>
+  </si>
+  <si>
+    <t>Validate List and Grid views when only one Product is displayed in the search results</t>
+  </si>
+  <si>
+    <t>1. Enter any existing product name into the 'Search' text box field 
+2. Click on the button having search icon 
+3. Select 'List' option 
+4. Click on the Image of the Product and name of the product
+5. Repeat Steps 1 to 2 and Select 'Grid' option
+6. Click on the Image of the Product and name of the product</t>
+  </si>
+  <si>
+    <t>1. Product Name: iMac
+2. Product Name: iphone</t>
+  </si>
+  <si>
+    <t>1. Single product should be dislayed in the List view without any problems and all the options (Add to Cart, Wish List and Compare Product) are working 
+2. User should be navigated to the Product Display Page of the product
+3. Single product should be dislayed in the Grid view without any problems and all the options (Add to Cart, Wish List and Compare Product) are working 
+4. User should be navigated to the Product Display Page of the product</t>
+  </si>
+  <si>
+    <t>Working as mentioned in the excepted results.</t>
+  </si>
+  <si>
+    <t>TC_SF_012</t>
+  </si>
+  <si>
+    <t>Validate List and Grid views when multiple Products are displayed in the search results</t>
+  </si>
+  <si>
+    <t>1. Enter the search criteria in the 'Search' text box field which can result in mutliple products
+2. Click on the button having search icon 
+3. Select 'List' option 
+4. Select 'Grid' option</t>
+  </si>
+  <si>
+    <t>Search Criteria: Mac</t>
+  </si>
+  <si>
+    <t>1. More than one products should be displayed in the search results page
+2. Multiple product should be dislayed in the List view without any problems and all the options (Add to Cart, Wish List and Compare Product) are working. Also User should be able to navigate to Product Displaye Page of products by clicking on Images and Product Name. 
+3. Multiple product should be dislayed in the Grid view without any problems and all the options (Add to Cart, Wish List and Compare Product) are working. Also User should be able to navigate to Product Displaye Page of products by clicking on Images and Product Name.</t>
+  </si>
+  <si>
+    <t>TC_SF_013</t>
+  </si>
+  <si>
+    <t>Validate navigating to Product Compare Page from Search Results page</t>
+  </si>
+  <si>
+    <t>1. Enter any existing product name into the 'Search' text box field
+2. Click on the button having search icon
+3. Click on the 'Product Compare' link</t>
+  </si>
+  <si>
+    <t>Product Name: iMac</t>
+  </si>
+  <si>
+    <t>1. User should be automatically navigated to the Product Compare Page</t>
+  </si>
+  <si>
+    <t>1. User is not navigated to the Product Compare Page automatically when click it.</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>BUG_008</t>
+  </si>
+  <si>
+    <t>TC_SF_014</t>
+  </si>
+  <si>
+    <t>Validate User is able to sort the Products displayed in the Search Results</t>
+  </si>
+  <si>
+    <t>1. Enter the search criteria in the 'Search' text box field which can result in mutliple products 
+2. Click on the button having search icon
+3. Select serveral options from the 'Sort By' dropdown</t>
+  </si>
+  <si>
+    <t>1. More than one product should be displayed in the search results page
+2. Products are sorted according to the options selected in the 'Sort By' dropdown field</t>
+  </si>
+  <si>
+    <t>1. More than one product are displayed in the search results page
+2. Products are sorted according to the options selected in the 'Sort By' dropdown field</t>
+  </si>
+  <si>
+    <t>TC_SF_015</t>
+  </si>
+  <si>
+    <t>Validate the User can select how many produts can be displayed in the Search Results</t>
+  </si>
+  <si>
+    <t>1. Enter the search criteria in the 'Search' text box field which can result in mutliple products
+2. Click on the button having search icon
+3. Select the number of Products to be displayed from the 'Show' dropdown</t>
+  </si>
+  <si>
+    <t>1. More than one product should be displayed in the search results page
+2. The selected number of products should be displayed in the current search page</t>
+  </si>
+  <si>
+    <t>1. More than one product is displayed in the search results page
+2. The selected number of products are displayed in the current search page</t>
+  </si>
+  <si>
+    <t>TC_SF_016</t>
+  </si>
+  <si>
+    <t>Validate 'Search' textbox field and the button having search icon are displayed on all the page of the Application</t>
+  </si>
+  <si>
+    <t>1. Navigate to all the pages of the Application</t>
+  </si>
+  <si>
+    <t>1. Search box field and the button with 'Search' icon should be displayed on all the page of the Application</t>
+  </si>
+  <si>
+    <t>1. Search box field and the button with 'Search' icon are displayed on all the page of the Application</t>
+  </si>
+  <si>
+    <t>TC_SF_017</t>
+  </si>
+  <si>
+    <t>Validate navigating to Search page from the Site Map page</t>
+  </si>
+  <si>
+    <t>1. Click on 'Site Map' link in the footer options
+2. Click on the 'Search' link from the 'Site Map' page</t>
+  </si>
+  <si>
+    <t>1. User should be navigated to 'Search' page</t>
+  </si>
+  <si>
+    <t>1. User is navigated to 'Search' page</t>
+  </si>
+  <si>
+    <t>TC_SF_018</t>
+  </si>
+  <si>
+    <t>Validate Breadcrumb of the 'Search' page</t>
+  </si>
+  <si>
+    <t>1. Enter any existing product name into the 'Search' text box field
+2. Click on the button having search icon 
+3. Check whether the Breadcrumb option</t>
+  </si>
+  <si>
+    <t>1. Breadcrumb option should be working correctly</t>
+  </si>
+  <si>
+    <t>1. Breadcrumb option is working correctly</t>
+  </si>
+  <si>
+    <t>TC_SF_019</t>
+  </si>
+  <si>
+    <t>Validate we can use all the options of Search functionality using the Keybaord keys</t>
+  </si>
+  <si>
+    <t>1. Press Tab and Enter keys to perform Search operation and select several options in the Search page</t>
+  </si>
+  <si>
+    <t>1. User should be able to perform Search operation and select several options in the Search page using the Keyboard keys Tab and Enter</t>
+  </si>
+  <si>
+    <t>1.'Search in subcategories and Search in Product description' option is not getting clicked using the enter key</t>
+  </si>
+  <si>
+    <t>BUG_009</t>
+  </si>
+  <si>
+    <t>TC_SF_020</t>
+  </si>
+  <si>
+    <t>Validate Page Heading, Page URL and Page Title of the 'Search' page</t>
+  </si>
+  <si>
+    <t>1. Enter any existing product name into the 'Search' text box field 
+2. Click on the button having search icon 
+3. Check the Page Heading, Page URL and Page Title of the 'Search' page</t>
+  </si>
+  <si>
+    <t>Product Name: imac</t>
+  </si>
+  <si>
+    <t>1. A proper Page Heading, Page URL and Page Title should be displayed for 'Search' page</t>
+  </si>
+  <si>
+    <t>1. A proper Page Heading, Page URL and Page Title are displayed for 'Search' page</t>
+  </si>
+  <si>
+    <t>TC_SF_021</t>
+  </si>
+  <si>
+    <t>Validate the UI of Search functionality and Search page options</t>
+  </si>
+  <si>
+    <t>1. Proper UI adhering to the UI checklist should be displayed for the complete Search functionality</t>
+  </si>
+  <si>
+    <t>1. Proper UI adhering to the UI checklist are displayed for the complete Search functionality</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1532,8 +1948,35 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1579,6 +2022,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA8A8A8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6D9EEB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AA84F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1693,7 +2154,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1780,6 +2241,39 @@
     <xf numFmtId="14" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1796,6 +2290,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4778,4 +5276,784 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408733F2-DC66-44CF-A962-A7ACD119C099}">
+  <dimension ref="B3:L25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="37.21875" customWidth="1"/>
+    <col min="5" max="5" width="30.5546875" customWidth="1"/>
+    <col min="6" max="6" width="39" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="8" max="8" width="47.88671875" customWidth="1"/>
+    <col min="9" max="9" width="36.5546875" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="44.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:12" ht="63" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>400</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="135" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>402</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>403</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>405</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>407</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>408</v>
+      </c>
+      <c r="J5" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K5" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="L5" s="38"/>
+    </row>
+    <row r="6" spans="2:12" ht="147.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>411</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>412</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>413</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>414</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>415</v>
+      </c>
+      <c r="J6" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K6" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="L6" s="38"/>
+    </row>
+    <row r="7" spans="2:12" ht="160.19999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>417</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>418</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>420</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>415</v>
+      </c>
+      <c r="J7" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K7" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="L7" s="38"/>
+    </row>
+    <row r="8" spans="2:12" ht="149.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>421</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>422</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>423</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>405</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>424</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>407</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>408</v>
+      </c>
+      <c r="J8" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K8" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="L8" s="38"/>
+    </row>
+    <row r="9" spans="2:12" ht="171.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>425</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>426</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>427</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>428</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>429</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>430</v>
+      </c>
+      <c r="J9" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K9" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="L9" s="38"/>
+    </row>
+    <row r="10" spans="2:12" ht="173.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>432</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>433</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>434</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>434</v>
+      </c>
+      <c r="J10" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" s="38"/>
+    </row>
+    <row r="11" spans="2:12" ht="241.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>436</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>424</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>407</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>408</v>
+      </c>
+      <c r="J11" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="L11" s="38"/>
+    </row>
+    <row r="12" spans="2:12" ht="286.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>439</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>441</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>443</v>
+      </c>
+      <c r="J12" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L12" s="38"/>
+    </row>
+    <row r="13" spans="2:12" ht="297" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>444</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>448</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>449</v>
+      </c>
+      <c r="J13" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K13" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L13" s="38"/>
+    </row>
+    <row r="14" spans="2:12" ht="294" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>450</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>451</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>452</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="H14" s="34" t="s">
+        <v>454</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>455</v>
+      </c>
+      <c r="J14" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L14" s="38"/>
+    </row>
+    <row r="15" spans="2:12" ht="293.39999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>456</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>458</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>459</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>460</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="J15" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="38"/>
+    </row>
+    <row r="16" spans="2:12" ht="347.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>464</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>465</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>466</v>
+      </c>
+      <c r="I16" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="J16" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L16" s="38"/>
+    </row>
+    <row r="17" spans="2:12" ht="191.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>467</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>468</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>470</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>471</v>
+      </c>
+      <c r="I17" s="34" t="s">
+        <v>472</v>
+      </c>
+      <c r="J17" s="39" t="s">
+        <v>473</v>
+      </c>
+      <c r="K17" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L17" s="40" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="261.60000000000002" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>476</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>477</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>428</v>
+      </c>
+      <c r="H18" s="34" t="s">
+        <v>478</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="J18" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L18" s="38"/>
+    </row>
+    <row r="19" spans="2:12" ht="282.60000000000002" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>480</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>481</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>428</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>483</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>484</v>
+      </c>
+      <c r="J19" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L19" s="38"/>
+    </row>
+    <row r="20" spans="2:12" ht="149.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>485</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>486</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>487</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>488</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>489</v>
+      </c>
+      <c r="J20" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L20" s="38"/>
+    </row>
+    <row r="21" spans="2:12" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>490</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>491</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>492</v>
+      </c>
+      <c r="G21" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>493</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>494</v>
+      </c>
+      <c r="J21" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L21" s="38"/>
+    </row>
+    <row r="22" spans="2:12" ht="211.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>495</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>496</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>497</v>
+      </c>
+      <c r="G22" s="33" t="s">
+        <v>424</v>
+      </c>
+      <c r="H22" s="34" t="s">
+        <v>498</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>499</v>
+      </c>
+      <c r="J22" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L22" s="38"/>
+    </row>
+    <row r="23" spans="2:12" ht="184.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>500</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>501</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>502</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>503</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>504</v>
+      </c>
+      <c r="J23" s="39" t="s">
+        <v>473</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L23" s="40" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="250.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>506</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>507</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>508</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>509</v>
+      </c>
+      <c r="H24" s="34" t="s">
+        <v>510</v>
+      </c>
+      <c r="I24" s="34" t="s">
+        <v>511</v>
+      </c>
+      <c r="J24" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L24" s="38"/>
+    </row>
+    <row r="25" spans="2:12" ht="167.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>512</v>
+      </c>
+      <c r="D25" s="34" t="s">
+        <v>513</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>405</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>509</v>
+      </c>
+      <c r="H25" s="34" t="s">
+        <v>514</v>
+      </c>
+      <c r="I25" s="34" t="s">
+        <v>515</v>
+      </c>
+      <c r="J25" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L25" s="38"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" display="https://demo.opencart.com/" xr:uid="{C9ED05F7-E01E-4D55-B150-D78E500CC67B}"/>
+    <hyperlink ref="E6" r:id="rId2" display="https://demo.opencart.com/" xr:uid="{F16B9759-A8D4-4F34-8732-92BCFF5940E7}"/>
+    <hyperlink ref="E7" r:id="rId3" display="https://demo.opencart.com/" xr:uid="{E00EE836-C056-473F-9CF8-7DB3A0B72522}"/>
+    <hyperlink ref="E8" r:id="rId4" display="https://demo.opencart.com/" xr:uid="{1FFDD352-E2F7-433C-9691-F93ACF1CFC78}"/>
+    <hyperlink ref="E9" r:id="rId5" display="https://demo.opencart.com/" xr:uid="{E96BDA40-0C6B-4D1D-AC25-871A07775D21}"/>
+    <hyperlink ref="E10" r:id="rId6" display="https://demo.opencart.com/" xr:uid="{5DBB437D-4406-451B-BC73-69E2B37D8821}"/>
+    <hyperlink ref="E11" r:id="rId7" display="https://demo.opencart.com/" xr:uid="{633690E5-8617-4A95-B758-5A674898405C}"/>
+    <hyperlink ref="E12" r:id="rId8" display="https://demo.opencart.com/" xr:uid="{83C1DD37-FADD-4BCF-AA68-D6C2C67FB9E8}"/>
+    <hyperlink ref="E13" r:id="rId9" display="https://demo.opencart.com/" xr:uid="{1087213A-A3D1-4A41-A6DB-6F4A1B87C18B}"/>
+    <hyperlink ref="E14" r:id="rId10" display="https://demo.opencart.com/" xr:uid="{A9571BD1-6E76-4F75-9758-F0E9F644C4AE}"/>
+    <hyperlink ref="E15" r:id="rId11" display="https://demo.opencart.com/" xr:uid="{CC101717-A668-4392-9FDA-FC3CCB6849DC}"/>
+    <hyperlink ref="E16" r:id="rId12" display="https://demo.opencart.com/" xr:uid="{6D8EAE86-4DF7-4C5D-A638-8253676B9E43}"/>
+    <hyperlink ref="E17" r:id="rId13" display="https://demo.opencart.com/" xr:uid="{88C569D9-ED91-42D7-BE71-FDF2BA3B064C}"/>
+    <hyperlink ref="E18" r:id="rId14" display="https://demo.opencart.com/" xr:uid="{C38ECDE3-F309-4F49-9A15-DE8697306822}"/>
+    <hyperlink ref="E19" r:id="rId15" display="https://demo.opencart.com/" xr:uid="{74498ED4-7A23-4622-B29F-088B99AB9974}"/>
+    <hyperlink ref="E20" r:id="rId16" display="https://demo.opencart.com/" xr:uid="{0A31B165-7220-4726-8793-27499F45A58F}"/>
+    <hyperlink ref="E21" r:id="rId17" display="https://demo.opencart.com/" xr:uid="{2EB64F77-D623-4571-90AD-85F9CA4ACCC4}"/>
+    <hyperlink ref="E22" r:id="rId18" display="https://demo.opencart.com/" xr:uid="{858FB2C0-2568-4648-9981-70B1C7C39B07}"/>
+    <hyperlink ref="E23" r:id="rId19" display="https://demo.opencart.com/" xr:uid="{1CE070D0-0C19-41ED-B7DC-EAF5B8FC1C1E}"/>
+    <hyperlink ref="E24" r:id="rId20" display="https://demo.opencart.com/" xr:uid="{E456D67E-C83A-4278-98FB-003BB30E0913}"/>
+    <hyperlink ref="E25" r:id="rId21" display="https://demo.opencart.com/" xr:uid="{C647D472-5446-47C9-93AE-CB9D173E182A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId22"/>
+</worksheet>
 </file>